--- a/data/raw/sales/Week 31/Fossil/Seller Sales (SP-API).xlsx
+++ b/data/raw/sales/Week 31/Fossil/Seller Sales (SP-API).xlsx
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G12" t="n">
-        <v>368488.98</v>
+        <v>356205.93</v>
       </c>
       <c r="H12" t="n">
         <v>11379</v>
